--- a/data/nzd0014/nzd0014.xlsx
+++ b/data/nzd0014/nzd0014.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D232"/>
+  <dimension ref="A1:D233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4566,6 +4566,24 @@
         <v>360.63</v>
       </c>
       <c r="D232" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>371.01</v>
+      </c>
+      <c r="C233" t="n">
+        <v>360.63</v>
+      </c>
+      <c r="D233" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -4582,7 +4600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B290"/>
+  <dimension ref="A1:B291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7485,6 +7503,16 @@
       </c>
       <c r="B290" t="n">
         <v>-0.24</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>-0.91</v>
       </c>
     </row>
   </sheetData>
@@ -7653,28 +7681,28 @@
         <v>0.1292</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03087136516699724</v>
+        <v>-0.03171214281475354</v>
       </c>
       <c r="J2" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K2" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002363529968639755</v>
+        <v>0.002515576890365523</v>
       </c>
       <c r="M2" t="n">
-        <v>4.161234583327161</v>
+        <v>4.148018199061765</v>
       </c>
       <c r="N2" t="n">
-        <v>25.91448566543923</v>
+        <v>25.80787181346787</v>
       </c>
       <c r="O2" t="n">
-        <v>5.09062723693645</v>
+        <v>5.080144861464865</v>
       </c>
       <c r="P2" t="n">
-        <v>372.9301311465413</v>
+        <v>372.9383255586145</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -7735,28 +7763,28 @@
         <v>0.0108</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.813457848889763</v>
+        <v>-1.840285235390679</v>
       </c>
       <c r="J3" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K3" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1910124236671908</v>
+        <v>0.1962503787784641</v>
       </c>
       <c r="M3" t="n">
-        <v>24.2494275902066</v>
+        <v>24.24799591577518</v>
       </c>
       <c r="N3" t="n">
-        <v>850.8783331747925</v>
+        <v>851.4534804556959</v>
       </c>
       <c r="O3" t="n">
-        <v>29.16981887456267</v>
+        <v>29.17967581135363</v>
       </c>
       <c r="P3" t="n">
-        <v>440.8172976121525</v>
+        <v>441.0925242048627</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -7794,7 +7822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D232"/>
+  <dimension ref="A1:D233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12821,6 +12849,28 @@
         </is>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>-34.724560933660364,173.09248170793285</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>-34.72528923643388,173.09256978125202</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0014/nzd0014.xlsx
+++ b/data/nzd0014/nzd0014.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D233"/>
+  <dimension ref="A1:D236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4584,6 +4584,60 @@
         <v>360.63</v>
       </c>
       <c r="D233" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>372.11</v>
+      </c>
+      <c r="C234" t="n">
+        <v>360.63</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>372.75</v>
+      </c>
+      <c r="C235" t="n">
+        <v>360.63</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:17:28+00:00</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>372.24</v>
+      </c>
+      <c r="C236" t="n">
+        <v>357.62</v>
+      </c>
+      <c r="D236" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -4600,7 +4654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B291"/>
+  <dimension ref="A1:B294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7513,6 +7567,36 @@
       </c>
       <c r="B291" t="n">
         <v>-0.91</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -7681,28 +7765,28 @@
         <v>0.1292</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03171214281475354</v>
+        <v>-0.03107976517728045</v>
       </c>
       <c r="J2" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K2" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002515576890365523</v>
+        <v>0.002480793834657158</v>
       </c>
       <c r="M2" t="n">
-        <v>4.148018199061765</v>
+        <v>4.098525788835282</v>
       </c>
       <c r="N2" t="n">
-        <v>25.80787181346787</v>
+        <v>25.48036351419084</v>
       </c>
       <c r="O2" t="n">
-        <v>5.080144861464865</v>
+        <v>5.047807792912765</v>
       </c>
       <c r="P2" t="n">
-        <v>372.9383255586145</v>
+        <v>372.9321279239052</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -7763,28 +7847,28 @@
         <v>0.0108</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.840285235390679</v>
+        <v>-1.91906621268211</v>
       </c>
       <c r="J3" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K3" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1962503787784641</v>
+        <v>0.2118413786364565</v>
       </c>
       <c r="M3" t="n">
-        <v>24.24799591577518</v>
+        <v>24.23314562920832</v>
       </c>
       <c r="N3" t="n">
-        <v>851.4534804556959</v>
+        <v>853.1105102304244</v>
       </c>
       <c r="O3" t="n">
-        <v>29.17967581135363</v>
+        <v>29.20805557085963</v>
       </c>
       <c r="P3" t="n">
-        <v>441.0925242048627</v>
+        <v>441.9047517939757</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -7822,7 +7906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D233"/>
+  <dimension ref="A1:D236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12871,6 +12955,72 @@
         </is>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>-34.72455870136078,173.09249341420482</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>-34.72528923643388,173.09256978125202</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>-34.72455740256778,173.0925002251264</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>-34.72528923643388,173.09256978125202</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:17:28+00:00</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>-34.72455843754347,173.09249479767328</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>-34.725295344816,173.0925377483525</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0014/nzd0014.xlsx
+++ b/data/nzd0014/nzd0014.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D236"/>
+  <dimension ref="A1:D237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4638,6 +4638,24 @@
         <v>357.62</v>
       </c>
       <c r="D236" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>371.2</v>
+      </c>
+      <c r="C237" t="n">
+        <v>357.62</v>
+      </c>
+      <c r="D237" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -4654,7 +4672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B294"/>
+  <dimension ref="A1:B295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7597,6 +7615,16 @@
       </c>
       <c r="B294" t="n">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -7765,28 +7793,28 @@
         <v>0.1292</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03107976517728045</v>
+        <v>-0.0317387272887729</v>
       </c>
       <c r="J2" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K2" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002480793834657158</v>
+        <v>0.002608974896193494</v>
       </c>
       <c r="M2" t="n">
-        <v>4.098525788835282</v>
+        <v>4.085014548543921</v>
       </c>
       <c r="N2" t="n">
-        <v>25.48036351419084</v>
+        <v>25.37567976155047</v>
       </c>
       <c r="O2" t="n">
-        <v>5.047807792912765</v>
+        <v>5.037427891449213</v>
       </c>
       <c r="P2" t="n">
-        <v>372.9321279239052</v>
+        <v>372.938620556332</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -7847,28 +7875,28 @@
         <v>0.0108</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.91906621268211</v>
+        <v>-1.945619628314526</v>
       </c>
       <c r="J3" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K3" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2118413786364565</v>
+        <v>0.2170895446800779</v>
       </c>
       <c r="M3" t="n">
-        <v>24.23314562920832</v>
+        <v>24.22810689756946</v>
       </c>
       <c r="N3" t="n">
-        <v>853.1105102304244</v>
+        <v>853.9090329470223</v>
       </c>
       <c r="O3" t="n">
-        <v>29.20805557085963</v>
+        <v>29.22172193672067</v>
       </c>
       <c r="P3" t="n">
-        <v>441.9047517939757</v>
+        <v>442.1800665742022</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -7906,7 +7934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D236"/>
+  <dimension ref="A1:D237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13021,6 +13049,28 @@
         </is>
       </c>
     </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>-34.72456054808142,173.09248372992533</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>-34.725295344816,173.0925377483525</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
